--- a/output/pdf_financials_xlsx/TTZ.xlsx
+++ b/output/pdf_financials_xlsx/TTZ.xlsx
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08733200000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.01483</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.022573</v>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.859438</v>
+        <v>-1.94677</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.509012</v>
+        <v>-0.523842</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.545208</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.859438</v>
+        <v>-1.94677</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.509012</v>
+        <v>-0.523842</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.533504</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-197.0196538823013</v>
+        <v>-206.2730521740696</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-50.05836727027045</v>
+        <v>-51.51681144568894</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-69.12509150745989</v>
@@ -34614,7 +34614,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
